--- a/TestFiles-prod-sanity/PolicyCancellationAgencyAdvance/[MLB]AdvanceStatement-PolicyCancellation-AgencyAdvance[Advance].xlsx
+++ b/TestFiles-prod-sanity/PolicyCancellationAgencyAdvance/[MLB]AdvanceStatement-PolicyCancellation-AgencyAdvance[Advance].xlsx
@@ -88,7 +88,7 @@
     <t>Integrity Health, LLC</t>
   </si>
   <si>
-    <t>ATENA-ADVX-PC-AA-TEST-B046</t>
+    <t>ATENA-ADVX-PC-AA-TEST-B051</t>
   </si>
   <si>
     <t>ROBERTS, PIPPIN</t>
